--- a/PV-study.xlsx
+++ b/PV-study.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/williamzhang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E054882B-9974-A34F-B5B2-08715DD5CAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE9731F-4D94-F445-B512-9DC4FCC218CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="760" windowWidth="27820" windowHeight="17240" xr2:uid="{E0EA9F27-B852-254F-8228-E04290B27A60}"/>
   </bookViews>
@@ -288,13 +288,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>16818.400000000001</c:v>
+                  <c:v>15541.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16739.2</c:v>
+                  <c:v>14985.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30817.3</c:v>
+                  <c:v>29485.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>41273.5</c:v>
@@ -318,10 +318,10 @@
                   <c:v>25880</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>18308.3</c:v>
+                  <c:v>18055</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12477.5</c:v>
+                  <c:v>11763.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -703,10 +703,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1208328.7200000002</c:v>
+                  <c:v>1213658.2200000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>372985.4</c:v>
+                  <c:v>367655.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2319,7 +2319,7 @@
         <v>264168.84999999998</v>
       </c>
       <c r="F1">
-        <v>16818.400000000001</v>
+        <v>15541.7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.2">
@@ -2337,7 +2337,7 @@
         <v>215517.91</v>
       </c>
       <c r="F2">
-        <v>16739.2</v>
+        <v>14985.1</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.2">
@@ -2355,7 +2355,7 @@
         <v>187155.44</v>
       </c>
       <c r="F3">
-        <v>30817.3</v>
+        <v>29485.9</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.2">
@@ -2499,7 +2499,7 @@
         <v>191172.89</v>
       </c>
       <c r="F11">
-        <v>18308.3</v>
+        <v>18055</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.2">
@@ -2517,7 +2517,7 @@
         <v>248642.75</v>
       </c>
       <c r="F12">
-        <v>12477.5</v>
+        <v>11763.5</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -2527,11 +2527,11 @@
       </c>
       <c r="F14">
         <f>SUM(F1:F12)</f>
-        <v>372985.4</v>
+        <v>367655.9</v>
       </c>
       <c r="G14">
         <f>F14*0.039/1000</f>
-        <v>14.546430600000001</v>
+        <v>14.338580100000001</v>
       </c>
       <c r="H14" t="s">
         <v>3</v>
@@ -2548,11 +2548,11 @@
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E16">
         <f>E14-F14</f>
-        <v>1208328.7200000002</v>
+        <v>1213658.2200000002</v>
       </c>
       <c r="F16">
         <f>F14</f>
-        <v>372985.4</v>
+        <v>367655.9</v>
       </c>
     </row>
   </sheetData>
